--- a/4.evidence/ITGC/SAP_SUIM_ActiveUserList_2025Q3.xlsx
+++ b/4.evidence/ITGC/SAP_SUIM_ActiveUserList_2025Q3.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="SUIM_ユーザ一覧" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="棚卸結果" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
-  </numFmts>
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,24 +32,13 @@
     </font>
     <font>
       <name val="Yu Gothic"/>
-      <i val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -74,7 +59,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -96,36 +81,75 @@
         <color rgb="00888888"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00888888"/>
+      </right>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00888888"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00888888"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,939 +515,1285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP SUIM / トランザクション: SUIM_REPT / 有効ユーザ一覧</t>
+          <t>SAP SUIM / Active User List Export - 2025Q3</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出力日時: 2025/12/05 10:15:42 (Q3定期棚卸用)</t>
-        </is>
-      </c>
+          <t>出力日時</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31 14:30:08</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>出力者: IT003 加藤 洋子 / 抽出条件: ユーザステータス=有効 / Client=100 本番</t>
-        </is>
-      </c>
+          <t>出力者</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IT003 加藤 洋子</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Transaction</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SUIM → User → Users by Logon Date</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>抽出条件</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Status = Active / Client = 100 (Production)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Valid on 2025-12-31</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>ユーザID</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>所属部門</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>付与ロール</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>有効期限</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>最終ログイン</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>最終ログイン日</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>作成日</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>CEO001</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>山本 健一</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>代表取締役</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>ALL_READ</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>2022-09-04</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>CFO001</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>渡辺 正博</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>管理本部</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>FI_MGR, CO_MGR, ALL_READ</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>2013-05-12</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>ACC001</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>佐藤 一郎</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>FI_MGR, CO_MGR</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>2012-04-20</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>ACC002</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>高橋 美咲</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>FI_SUP, GL_POST</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2019-06-06</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>ACC003</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>伊藤 健太</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>CO_SUP</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>2010-09-24</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>ACC004</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>中村 真理</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>経理部</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>FI_USER, GL_POST</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>42095</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>2014-10-17</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>ACC005</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>小川 由紀</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>FI_USER</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>2012-02-10</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>ACC006</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>石井 健</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>FI_USER, AP_USER</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>2016-03-13</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>SLS001</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>田中 太郎</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>営業本部</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>SD_MGR</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>2018-11-13</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>SLS002</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>斎藤 次郎</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>営業本部</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>SD_SUP</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>2014-08-08</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>SLS003</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>藤田 修</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>営業本部</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>SD_SUP</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>2019-02-25</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>SLS004</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>松本 香織</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>営業本部</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>SD_USER</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>41730</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>2013-12-04</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>SLS005</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>井上 大輔</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>営業本部</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>SD_USER</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>43191</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>2022-01-20</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>PUR001</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>木村 浩二</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>購買部</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>MM_MGR, PO_APPROVE</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>2022-03-26</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>PUR002</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>林 真由美</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>購買部</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>MM_SUP, PO_APPROVE</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>2017-11-13</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>PUR003</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>清水 智明</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>購買部</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>MM_USER, PO_CREATE</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>41365</v>
-      </c>
-      <c r="H18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>PUR004</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>山田 純一</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>購買部</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>MM_USER, PO_CREATE, PO_APPROVE</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>42826</v>
-      </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>2019-10-13</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>※ SoD違反: PO_CREATE+PO_APPROVE (要改善)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>MFG001</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>森 和雄</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>製造本部</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>PP_MGR</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>2013-05-07</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>MFG002</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>池田 昌夫</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>製造本部</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>PP_SUP</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2011-11-07</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>WHS001</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>橋本 明</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>製造本部</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>WM_SUP</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>2022-08-13</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>IT001</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>岡田 宏</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>情シス部</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>BASIS, ALL_READ</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>40269</v>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>2021-11-13</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>特権ID</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>IT002</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>吉田 雅彦</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>情シス部</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>BASIS</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>2021-02-16</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>特権ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>IT003</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>加藤 洋子</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>情シス部</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>45996</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>41000</v>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>SLS099</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>退職者A</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>(退職)営業本部</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>SD_USER</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>45930</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>43191</v>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>※ 退職2025/9/30、停止2025/10/11（11日遅延）— 不備</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>PUR099</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>退職者B</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>(退職)購買部</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>MM_USER</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>無期限</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>45976</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>42826</v>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>※ 退職2025/11/15、停止2025/12/3（18日遅延）— 不備</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>※ 本一覧は四半期定期棚卸のため出力。全ユーザ245名中、経理・営業・購買・情シス部の18名を抜粋。</t>
-        </is>
-      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>2022-01-22</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>IT004</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>西田 徹</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>情シス部</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>HELPDESK</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>2016-03-09</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>HR001</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>近藤 文子</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>HR_MGR</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>2013-01-19</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>HR002</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>野村 淳</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>人事部</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>HR_USER</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>2022-12-27</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>GA001</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>前田 美香</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>総務部</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>GA_MGR</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>IA001</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>長谷川 剛</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>内部監査室</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>ALL_READ</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>2018-05-27</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>IA002</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>大塚 美穂</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>内部監査室</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>ALL_READ</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>無期限</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>2019-12-01</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Q3アクセス権棚卸結果（2025/12実施）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>※ 本棚卸はQ3（2025/12）分 / 完了日: 2025/12/22</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>⚠ 本エビデンスだけでは抽出条件・抽出日時の完全性が不明（内部監査指摘事項）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>部門</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>対象ユーザ数</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>継続必要</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>削除依頼</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>未レビュー</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>部門長承認</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>経理部</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>佐藤 一郎 [印] 2025/12/18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>営業本部</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>田中 太郎 [印] 2025/12/19</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>購買部</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>木村 浩二 [印] 2025/12/17</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>製造本部</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>森 和雄 [印] 2025/12/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>情シス部</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>岡田 宏 [印] 2025/12/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>各部門長 [印]</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/4.evidence/ITGC/SAP_SUIM_ActiveUserList_2025Q3.xlsx
+++ b/4.evidence/ITGC/SAP_SUIM_ActiveUserList_2025Q3.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP SUIM / Active User List Export - 2025Q3</t>
+          <t>SAP SUIM / Active User List Export - 2025Q3 [※ヘッダ情報一部欠落]</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-12-31 14:30:08</t>
+          <t>(判別不能 - 再出力依頼中)</t>
         </is>
       </c>
       <c r="D2" s="4" t="n"/>
@@ -598,7 +598,7 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Status = Active / Client = 100 (Production)</t>
+          <t>(条件指定の証跡なし - 再出力依頼中)</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -1783,8 +1783,8 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A2:B2"/>
